--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -15346,12 +15346,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -15385,81 +15385,95 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="O92" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="R92" t="n">
-        <v>0.01203316015763142</v>
+        <v>0.1495180868525335</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15486,17 +15500,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -15521,7 +15535,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -15530,81 +15544,170 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="O93" t="n">
-        <v>23</v>
-      </c>
-      <c r="R93" t="n">
-        <v>0.006589587705369587</v>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Vibrioinfektion</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Vibrio category.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>1</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15769,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -15675,13 +15778,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="O94" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="R94" t="n">
-        <v>0.00802210677175428</v>
+        <v>0.01203316015763142</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -15811,7 +15914,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -15820,13 +15923,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R95" t="n">
-        <v>0.006303083892092647</v>
+        <v>0.006589587705369587</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -15956,7 +16059,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -15965,13 +16068,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O96" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="R96" t="n">
-        <v>0.008881618211585096</v>
+        <v>0.00802210677175428</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16071,12 +16174,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -16101,22 +16204,22 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>0.006303083892092647</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -16149,42 +16252,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16216,12 +16319,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -16246,22 +16349,22 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="R98" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.008881618211585096</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -16294,42 +16397,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16361,12 +16464,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -16413,82 +16516,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16515,212 +16604,516 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>2</v>
+      </c>
+      <c r="O100" t="n">
+        <v>2</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>D126</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Vibriosis</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>弧菌病</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N100" t="n">
+      <c r="N102" t="n">
         <v>0</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="U102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_603_MONTHLY</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
+      <c r="V102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_603_MONTHLY</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
+      <c r="W102" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>Vibrioinfeksjon</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA100" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
+      <c r="AB102" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
+      <c r="AC102" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD100" t="inlineStr">
+      <c r="AD102" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE100" t="inlineStr">
+      <c r="AE102" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF100" t="inlineStr">
+      <c r="AF102" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG100" t="inlineStr">
+      <c r="AG102" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH100" t="inlineStr">
+      <c r="AH102" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI100" t="inlineStr">
+      <c r="AI102" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ100" t="inlineStr">
+      <c r="AJ102" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK100" t="inlineStr">
+      <c r="AK102" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AM102" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN100" t="b">
+      <c r="AN102" t="b">
         <v>1</v>
       </c>
-      <c r="AO100" t="inlineStr">
+      <c r="AO102" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP100" t="inlineStr">
+      <c r="AP102" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ100" t="inlineStr">
+      <c r="AQ102" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS100" t="inlineStr">
+      <c r="AS102" t="inlineStr">
         <is>
           <t>SER_NO_FHI_603_MONTHLY</t>
         </is>
       </c>
-      <c r="AT100" t="n">
+      <c r="AT102" t="n">
         <v>1</v>
       </c>
-      <c r="AU100" t="inlineStr">
+      <c r="AU102" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV100" t="inlineStr">
+      <c r="AV102" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW100" t="inlineStr">
+      <c r="AW102" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
+      <c r="AX102" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY100" t="inlineStr">
+      <c r="AY102" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA100" t="inlineStr">
+      <c r="BA102" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB100" t="inlineStr">
+      <c r="BB102" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC100" t="inlineStr">
+      <c r="BC102" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -16842,7 +17235,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -16852,7 +17245,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -16872,7 +17265,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -16904,7 +17297,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>731</v>
+        <v>748</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -14992,13 +14992,13 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O90" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R90" t="n">
-        <v>0.1945873408375057</v>
+        <v>0.2122770990954608</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -15151,10 +15151,10 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U91" t="inlineStr">
         <is>
@@ -16793,13 +16793,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -16952,10 +16952,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -17119,6 +17119,151 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>19</v>
+      </c>
+      <c r="O103" t="n">
+        <v>19</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.005443572452261832</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17152,7 +17297,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -17235,7 +17380,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -17245,7 +17390,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -17297,7 +17442,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>750</v>
+        <v>769</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -13992,13 +13992,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R83" t="n">
-        <v>0.03305530637567811</v>
+        <v>0.0367281181951979</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -16648,13 +16648,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -16648,13 +16648,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R100" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -16793,13 +16793,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R101" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -16952,10 +16952,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -14847,13 +14847,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R89" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16648,13 +16648,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R100" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17259,6 +17259,151 @@
         </is>
       </c>
       <c r="BC103" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>20</v>
+      </c>
+      <c r="O104" t="n">
+        <v>20</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.00573007626553877</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -17297,7 +17442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -17380,7 +17525,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -17390,7 +17535,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -17442,7 +17587,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>776</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -14847,13 +14847,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R89" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16648,13 +16648,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O100" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R100" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>798</v>
+        <v>806</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -16648,13 +16648,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O100" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R100" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -16793,13 +16793,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R101" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -16952,10 +16952,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O102" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -17404,6 +17404,151 @@
         </is>
       </c>
       <c r="BC104" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>29</v>
+      </c>
+      <c r="O105" t="n">
+        <v>29</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.008308610585031217</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -17442,7 +17587,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -17525,7 +17670,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -17535,7 +17680,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -17587,7 +17732,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>806</v>
+        <v>839</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -16503,13 +16503,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -16648,13 +16648,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O100" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R100" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17551,6 +17551,296 @@
       <c r="BC105" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>19</v>
+      </c>
+      <c r="O106" t="n">
+        <v>19</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.005443572452261832</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
+      <c r="AT106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17877,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -17670,7 +17960,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -17680,7 +17970,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -17732,7 +18022,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>839</v>
+        <v>874</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -16503,13 +16503,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O99" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R99" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.05141936547327706</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -24875,13 +24875,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O158" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R158" t="n">
-        <v>0.03682142855204888</v>
+        <v>0.03875939847584092</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -26249,7 +26249,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1782,6 +1817,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1918,6 +1958,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2063,6 +2108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2446,7 +2496,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2997,6 +3047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3145,6 +3200,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3293,6 +3353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3441,6 +3506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3589,6 +3659,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3737,6 +3812,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3882,6 +3962,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4027,6 +4112,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4163,6 +4253,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4308,6 +4403,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4444,6 +4544,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4580,6 +4685,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4725,6 +4835,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4870,6 +4985,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5015,6 +5135,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5398,7 +5523,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -5949,6 +6074,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6097,6 +6227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6245,6 +6380,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6393,6 +6533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6541,6 +6686,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6686,6 +6836,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6831,6 +6986,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6976,6 +7136,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7121,6 +7286,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7257,6 +7427,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7402,6 +7577,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7547,6 +7727,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7683,6 +7868,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7828,6 +8018,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8211,7 +8406,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -8762,6 +8957,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8910,6 +9110,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9058,6 +9263,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9206,6 +9416,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9351,6 +9566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9496,6 +9716,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9641,6 +9866,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9777,6 +10007,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9922,6 +10157,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10067,6 +10307,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10203,6 +10448,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10348,6 +10598,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10493,6 +10748,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10638,6 +10898,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11021,7 +11286,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -11572,6 +11837,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11720,6 +11990,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11868,6 +12143,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12016,6 +12296,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12161,6 +12446,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12306,6 +12596,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12451,6 +12746,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12596,6 +12896,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12741,6 +13046,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12877,6 +13187,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13022,6 +13337,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13158,6 +13478,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13294,6 +13619,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13439,6 +13769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13822,7 +14157,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -14373,6 +14708,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14521,6 +14861,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14669,6 +15014,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14817,6 +15167,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14962,6 +15317,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15107,6 +15467,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15252,6 +15617,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15397,6 +15767,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15533,6 +15908,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15678,6 +16058,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15814,6 +16199,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15959,6 +16349,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16095,6 +16490,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16240,6 +16640,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16385,6 +16790,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16768,7 +17178,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -17316,6 +17726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17461,6 +17876,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17606,6 +18026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17751,6 +18176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17896,6 +18326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18041,6 +18476,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18177,6 +18617,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18322,6 +18767,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18458,6 +18908,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18603,6 +19058,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18739,6 +19199,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18884,6 +19349,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19020,6 +19490,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19165,6 +19640,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19548,7 +20028,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -20096,6 +20576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20241,6 +20726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20386,6 +20876,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20531,6 +21026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20663,17 +21163,22 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R130" t="n">
-        <v>0.0367281181951979</v>
+        <v>0.04040093001471769</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -20821,6 +21326,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20957,6 +21467,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21102,6 +21617,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21238,6 +21758,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21383,6 +21908,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21528,6 +22058,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21664,6 +22199,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21800,6 +22340,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21945,6 +22490,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22328,7 +22878,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -22876,6 +23426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23021,6 +23576,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23166,6 +23726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23311,6 +23876,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23456,6 +24026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23588,17 +24163,22 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O149" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R149" t="n">
-        <v>0.05141936547327706</v>
+        <v>0.04774655365375727</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -23746,6 +24326,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23891,6 +24476,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24036,6 +24626,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24172,6 +24767,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24317,6 +24917,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24462,6 +25067,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24598,6 +25208,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24743,6 +25358,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24875,17 +25495,22 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O158" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R158" t="n">
-        <v>0.03875939847584092</v>
+        <v>0.04069736839963296</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -25020,13 +25645,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O159" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R159" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -25179,10 +25804,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O160" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -25271,7 +25896,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -25374,12 +25999,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -25404,7 +26029,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -25413,81 +26038,95 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="O161" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="R161" t="n">
-        <v>0.005443572452261832</v>
+        <v>0.1121385651394002</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25514,17 +26153,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -25549,7 +26188,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -25558,81 +26197,170 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O162" t="n">
-        <v>20</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0.00573007626553877</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Vibrioinfektion</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined Vibrio category.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_VIBRIO</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25694,7 +26422,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -25703,17 +26431,22 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="O163" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="R163" t="n">
-        <v>0.008308610585031217</v>
+        <v>0.005443572452261832</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -25839,7 +26572,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -25848,17 +26581,22 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O164" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R164" t="n">
-        <v>0.005443572452261832</v>
+        <v>0.00573007626553877</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -25954,12 +26692,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -25984,26 +26722,31 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>0.008308610585031217</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -26032,42 +26775,885 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>19</v>
+      </c>
+      <c r="O166" t="n">
+        <v>19</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.005443572452261832</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" t="n">
+        <v>1</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW165" t="inlineStr">
+      <c r="AW167" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX165" t="inlineStr">
+      <c r="AX167" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY165" t="inlineStr">
+      <c r="AY167" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ165" t="inlineStr">
+      <c r="AZ167" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA165" t="inlineStr">
+      <c r="BA167" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB165" t="inlineStr">
+      <c r="BB167" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC165" t="inlineStr">
+      <c r="BC167" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="n">
+        <v>1</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>1</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Vibrioinfeksjon</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_603_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV169" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB169" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC169" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>18</v>
+      </c>
+      <c r="O170" t="n">
+        <v>18</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.005157068638984894</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26104,7 +27690,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -26187,7 +27773,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -26197,7 +27783,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -26217,7 +27803,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -26249,7 +27835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1008</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -27031,13 +27031,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R167" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -24163,13 +24163,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O149" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R149" t="n">
-        <v>0.04774655365375727</v>
+        <v>0.05509217729279685</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25495,13 +25495,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O158" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R158" t="n">
-        <v>0.04069736839963296</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27181,13 +27181,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R168" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -27340,10 +27340,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O169" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1043</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -3036,9 +3036,6 @@
       <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -3189,9 +3186,6 @@
       <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -3342,9 +3336,6 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -3495,9 +3486,6 @@
       <c r="O19" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -3648,9 +3636,6 @@
       <c r="O20" t="n">
         <v>6</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -6063,9 +6048,6 @@
       <c r="O35" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -6216,9 +6198,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -6369,9 +6348,6 @@
       <c r="O37" t="n">
         <v>4</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -6522,9 +6498,6 @@
       <c r="O38" t="n">
         <v>6</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -8946,9 +8919,6 @@
       <c r="O53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -9099,9 +9069,6 @@
       <c r="O54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -9252,9 +9219,6 @@
       <c r="O55" t="n">
         <v>5</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -9405,9 +9369,6 @@
       <c r="O56" t="n">
         <v>8</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.002292030506215508</v>
       </c>
@@ -11826,9 +11787,6 @@
       <c r="O71" t="n">
         <v>8</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.002292030506215508</v>
       </c>
@@ -11979,9 +11937,6 @@
       <c r="O72" t="n">
         <v>6</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -12132,9 +12087,6 @@
       <c r="O73" t="n">
         <v>7</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -12285,9 +12237,6 @@
       <c r="O74" t="n">
         <v>13</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.003724549572600201</v>
       </c>
@@ -14697,9 +14646,6 @@
       <c r="O89" t="n">
         <v>11</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.003151541946046324</v>
       </c>
@@ -14850,9 +14796,6 @@
       <c r="O90" t="n">
         <v>8</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.002292030506215508</v>
       </c>
@@ -15003,9 +14946,6 @@
       <c r="O91" t="n">
         <v>3</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -15156,9 +15096,6 @@
       <c r="O92" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -27652,6 +27589,156 @@
         </is>
       </c>
       <c r="BC170" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>16</v>
+      </c>
+      <c r="O171" t="n">
+        <v>16</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.004584061012431017</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -27690,7 +27777,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -27773,7 +27860,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -27783,7 +27870,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -27835,7 +27922,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1049</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -44698,13 +44698,13 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O318" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R318" t="n">
-        <v>0.01554201126394116</v>
+        <v>0.01673755059193663</v>
       </c>
       <c r="U318" t="inlineStr">
         <is>
@@ -56920,13 +56920,13 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R405" t="n">
-        <v>0.001195539327995473</v>
+        <v>0.002391078655990946</v>
       </c>
       <c r="U405" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -56497,13 +56497,13 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O402" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R402" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="AA402" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -54370,13 +54370,13 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O387" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R387" t="n">
-        <v>0.009564314623963786</v>
+        <v>0.01075985395195926</v>
       </c>
       <c r="U387" t="inlineStr">
         <is>
@@ -57138,6 +57138,150 @@
       <c r="BC406" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>1</v>
+      </c>
+      <c r="O407" t="n">
+        <v>1</v>
+      </c>
+      <c r="R407" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO407" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP407" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS407" t="inlineStr">
+        <is>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+        </is>
+      </c>
+      <c r="AT407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV407" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW407" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX407" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY407" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA407" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB407" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC407" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -57174,7 +57318,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -57257,7 +57401,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10">
@@ -57267,7 +57411,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11">
@@ -57319,7 +57463,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d126/2026-2029.xlsx
+++ b/diseases/d126/2026-2029.xlsx
@@ -39427,13 +39427,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O280" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R280" t="n">
-        <v>0.04040093001471769</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
@@ -56458,12 +56458,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -56497,13 +56497,13 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O402" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R402" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.06611061275135623</v>
       </c>
       <c r="AA402" t="inlineStr">
         <is>
@@ -56526,42 +56526,42 @@
       </c>
       <c r="AV402" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW402" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX402" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY402" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ402" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA402" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB402" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC402" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -56593,12 +56593,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -56632,18 +56632,13 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O403" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R403" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="U403" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
+        <v>0.009689849618960231</v>
       </c>
       <c r="AA403" t="inlineStr">
         <is>
@@ -56652,7 +56647,7 @@
       </c>
       <c r="AO403" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP403" t="inlineStr">
@@ -56660,52 +56655,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS403" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_603_MONTHLY</t>
-        </is>
-      </c>
+      <c r="AS403" t="inlineStr"/>
       <c r="AT403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV403" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW403" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX403" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY403" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ403" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA403" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB403" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC403" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -56737,12 +56728,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -56767,7 +56758,7 @@
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M404" t="inlineStr">
@@ -56776,22 +56767,22 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R404" t="n">
-        <v>0.002391078655990946</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>SER_NO_FHI_603_MONTHLY</t>
         </is>
       </c>
       <c r="AA404" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO404" t="inlineStr">
@@ -56806,7 +56797,7 @@
       </c>
       <c r="AS404" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>SER_NO_FHI_603_MONTHLY</t>
         </is>
       </c>
       <c r="AT404" t="n">
@@ -56814,42 +56805,42 @@
       </c>
       <c r="AV404" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW404" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ404" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA404" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB404" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC404" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -56911,7 +56902,7 @@
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M405" t="inlineStr">
@@ -57025,12 +57016,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>US-NV</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Nevada, United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -57055,7 +57046,7 @@
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
@@ -57064,22 +57055,22 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O406" t="n">
-        <v>1</v>
-      </c>
-      <c r="P406" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R406" t="n">
+        <v>0.002391078655990946</v>
       </c>
       <c r="U406" t="inlineStr">
         <is>
-          <t>HOLD_US_6ab0bc2327a7a5b9f487161c73e8</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AA406" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO406" t="inlineStr">
@@ -57094,7 +57085,7 @@
       </c>
       <c r="AS406" t="inlineStr">
         <is>
-          <t>HOLD_US_6ab0bc2327a7a5b9f487161c73e8</t>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
         </is>
       </c>
       <c r="AT406" t="n">
@@ -57102,42 +57093,42 @@
       </c>
       <c r="AV406" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW406" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ406" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA406" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB406" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC406" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -57169,12 +57160,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US-NV</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Nevada, United States</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -57199,7 +57190,7 @@
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
@@ -57213,17 +57204,17 @@
       <c r="O407" t="n">
         <v>1</v>
       </c>
-      <c r="R407" t="n">
-        <v>0.001195539327995473</v>
+      <c r="P407" t="n">
+        <v>1</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_US_6ab0bc2327a7a5b9f487161c73e8</t>
         </is>
       </c>
       <c r="AA407" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO407" t="inlineStr">
@@ -57238,7 +57229,7 @@
       </c>
       <c r="AS407" t="inlineStr">
         <is>
-          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+          <t>HOLD_US_6ab0bc2327a7a5b9f487161c73e8</t>
         </is>
       </c>
       <c r="AT407" t="n">
@@ -57246,40 +57237,184 @@
       </c>
       <c r="AV407" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW407" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX407" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="AY407" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="BA407" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="BB407" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+        </is>
+      </c>
+      <c r="BC407" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>vibriosis</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>D126</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Vibriosis</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>弧菌病</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>1</v>
+      </c>
+      <c r="O408" t="n">
+        <v>1</v>
+      </c>
+      <c r="R408" t="n">
+        <v>0.001195539327995473</v>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO408" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP408" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS408" t="inlineStr">
+        <is>
+          <t>HOLD_DE_16f5df972f268cf6814c42ea1fa0</t>
+        </is>
+      </c>
+      <c r="AT408" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV408" t="inlineStr">
+        <is>
           <t>rki_survstat</t>
         </is>
       </c>
-      <c r="AW407" t="inlineStr">
+      <c r="AW408" t="inlineStr">
         <is>
           <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
-      <c r="AX407" t="inlineStr">
+      <c r="AX408" t="inlineStr">
         <is>
           <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
-      <c r="AY407" t="inlineStr">
+      <c r="AY408" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
       </c>
-      <c r="AZ407" t="inlineStr">
+      <c r="AZ408" t="inlineStr">
         <is>
           <t>rki_survstat</t>
         </is>
       </c>
-      <c r="BA407" t="inlineStr">
+      <c r="BA408" t="inlineStr">
         <is>
           <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
-      <c r="BB407" t="inlineStr">
+      <c r="BB408" t="inlineStr">
         <is>
           <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
-      <c r="BC407" t="inlineStr">
+      <c r="BC408" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -57401,7 +57536,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10">
@@ -57411,7 +57546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11">
@@ -57463,7 +57598,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>811</v>
+        <v>831</v>
       </c>
     </row>
     <row r="16">
